--- a/data/trans_dic/IP1010-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastonos mentales</t>
+          <t>Menores que padecen trastonos mentales (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,87</t>
+          <t>0,19; 1,8</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1228,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 7,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1247,27 +1248,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,36</t>
+          <t>0,41; 3,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,89</t>
+          <t>0,07; 0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,31</t>
+          <t>0,2; 1,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,23</t>
+          <t>0,22; 1,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,74</t>
+          <t>0,2; 0,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,7</t>
+          <t>0,14; 0,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,68</t>
+          <t>0,16; 0,72</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastonos mentales (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4049</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3810</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2539</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3239</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4384</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3301</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2234</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4352</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4476</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3649</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4364</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5195</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5111</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4839</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5044</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5121</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3655</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2637</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4462</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4611</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3535</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5443</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>517; 5024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3113</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3841</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4352</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3426</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>601; 4983</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4346</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3991</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4856</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4540</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>445; 6164</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2991</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1368; 8144</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>685; 6641</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1556; 9902</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2586; 9648</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2003; 9603</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2177; 9977</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1010-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Clase-trans_dic.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
     </row>
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,8</t>
+          <t>0,19; 1,88</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,63</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,38</t>
+          <t>0,41; 3,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,91</t>
+          <t>0,07; 0,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,19</t>
+          <t>0,2; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,1; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,4</t>
+          <t>0,28; 1,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,73</t>
+          <t>0,19; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,69</t>
+          <t>0,14; 0,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,72</t>
+          <t>0,14; 0,7</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4049</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3810</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2539</t>
+          <t>0; 2506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3239</t>
+          <t>0; 2870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 3253</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2234</t>
+          <t>0; 2705</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4352</t>
+          <t>0; 5122</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3649</t>
+          <t>0; 4289</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3235</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2143,32 +2143,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4364</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5195</t>
+          <t>0; 4616</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5111</t>
+          <t>0; 5069</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4839</t>
+          <t>0; 4887</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5044</t>
+          <t>0; 4645</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5121</t>
+          <t>0; 5476</t>
         </is>
       </c>
     </row>
@@ -2296,42 +2296,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 3657</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2637</t>
+          <t>0; 2654</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4462</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4611</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3535</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5443</t>
+          <t>0; 5651</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>517; 5024</t>
+          <t>521; 5238</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3113</t>
+          <t>0; 2977</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>0; 3805</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4352</t>
+          <t>0; 3770</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3426</t>
+          <t>0; 2927</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>601; 4983</t>
+          <t>601; 4937</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4346</t>
+          <t>0; 4371</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4540</t>
+          <t>0; 4219</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>445; 6164</t>
+          <t>444; 5745</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2991</t>
+          <t>0; 3386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1368; 8144</t>
+          <t>1364; 8725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>685; 6641</t>
+          <t>689; 6015</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1556; 9902</t>
+          <t>1998; 8918</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2586; 9648</t>
+          <t>2530; 9774</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2003; 9603</t>
+          <t>2002; 10277</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2177; 9977</t>
+          <t>1885; 9668</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1010-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
     </row>
@@ -855,22 +855,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,88</t>
+          <t>0,19; 1,87</t>
         </is>
       </c>
     </row>
@@ -1175,27 +1175,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,35</t>
+          <t>0,41; 3,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,2; 1,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,85</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,21; 1,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,27</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,84</t>
+          <t>0,07; 0,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,26</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,74</t>
+          <t>0,15; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,74</t>
+          <t>0,15; 0,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,7</t>
+          <t>0,15; 0,68</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3259</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2506</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2870</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2699</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3253</t>
+          <t>0; 3100</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2705</t>
+          <t>0; 2254</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>0; 4936</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4190</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4289</t>
+          <t>0; 3578</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4439</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4328</t>
+          <t>0; 3228</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 4517</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4646</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5476</t>
+          <t>0; 5074</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3142</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3657</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>0; 4584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>0; 4923</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 2150</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3227</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5651</t>
+          <t>0; 5567</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>521; 5238</t>
+          <t>525; 5211</t>
         </is>
       </c>
     </row>
@@ -2348,22 +2348,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2401,27 +2401,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>756</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2977</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3805</t>
+          <t>0; 3249</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3770</t>
+          <t>0; 3029</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2927</t>
+          <t>0; 3744</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>601; 4937</t>
+          <t>598; 4941</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4371</t>
+          <t>0; 5254</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3991</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3991</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4219</t>
+          <t>1371; 8965</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>444; 5745</t>
+          <t>650; 6042</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3386</t>
+          <t>1521; 8718</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1364; 8725</t>
+          <t>0; 4388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>689; 6015</t>
+          <t>445; 6032</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1998; 8918</t>
+          <t>0; 3321</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2530; 9774</t>
+          <t>2005; 9805</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2002; 10277</t>
+          <t>2017; 9708</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1885; 9668</t>
+          <t>2048; 9456</t>
         </is>
       </c>
     </row>
